--- a/jogos_2025-01-10.xlsx
+++ b/jogos_2025-01-10.xlsx
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AD7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['19', '38', '61']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['89', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.53</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['90+3', '7', '85', '90+9']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['39', '55']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45667.41666666666</v>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.53</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AD8" t="n">
         <v>2.38</v>
       </c>
-      <c r="T8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '59']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['45+2', '90+8']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45667.41666666666</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AD10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['45+2', '90+8']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.4</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AJ10" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['19', '38', '61']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['89', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45667.41666666666</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1869,31 +1869,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['52', '90+6']</t>
+          <t>['90+3', '7', '85', '90+9']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['39', '55']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ11" t="n">
         <v>3.1</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
         <v>2.3</v>
       </c>
       <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.09</v>
-      </c>
       <c r="U12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.67</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['45', '59']</t>
+          <t>['52', '90+6']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45667.41666666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.7</v>
-      </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
         <v>1.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['1', '13', '48']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['72', '90+5']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45667.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC24" t="n">
         <v>1.67</v>
       </c>
       <c r="AD24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['1', '13', '48']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['72', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45667.58333333334</v>
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
         <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S27" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
         <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45667.64583333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T28" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['41', '47']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['33', '85']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O29" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.95</v>
       </c>
-      <c r="O29" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z29" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['30', '49', '72', '81']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['33', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>2.09</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="O30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X30" t="n">
         <v>3.1</v>
       </c>
-      <c r="P30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Y30" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['77', '88']</t>
+          <t>['41', '47']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['23', '45+5']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4399,10 +4399,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
         <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T31" t="n">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V31" t="n">
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X31" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N32" t="n">
-        <v>5.75</v>
+        <v>2.7</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S32" t="n">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="T32" t="n">
-        <v>2.9</v>
+        <v>3.54</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Y32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['30', '49', '72', '81']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4642,16 +4642,16 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M33" t="n">
         <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
         <v>2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
         <v>2.9</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S34" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V34" t="n">
         <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X34" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['77', '88']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['23', '45+5']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45667.64583333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,31 +4926,31 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
         <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U35" t="n">
         <v>1.4</v>
@@ -4962,16 +4962,16 @@
         <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AA35" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AB35" t="n">
         <v>1.33</v>
@@ -4980,29 +4980,29 @@
         <v>1.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '90+3']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['27', '47', '87']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5029,16 +5029,16 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T36" t="n">
         <v>3</v>
       </c>
-      <c r="O36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.75</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,43 +5313,43 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="P38" t="n">
         <v>2.05</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
         <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y38" t="n">
         <v>2</v>
@@ -5358,38 +5358,38 @@
         <v>1.73</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AB38" t="n">
         <v>1.25</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AD38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.77</v>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI38" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X39" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['22', '41', '82']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['17', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AI39" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,25 +5545,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="M40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O40" t="n">
         <v>3.5</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X40" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.5</v>
+        <v>3.19</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '47', '87']</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>2</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>3</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['11']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['22', '41', '82']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45667.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA43" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.6</v>
+        <v>1.66</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45667.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,25 +6061,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lucchese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
         <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
         <v>1.44</v>
@@ -6111,31 +6111,31 @@
         <v>2.63</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U44" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X44" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AC44" t="n">
         <v>1.91</v>
@@ -6145,25 +6145,25 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['47', '70']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['14', '42', '71']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45667.6875</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,109 +6190,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Lucchese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
         <v>3</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
       <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="O45" t="n">
         <v>3.25</v>
       </c>
       <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W45" t="n">
+      <c r="AD45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['47', '70']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['14', '42', '71']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.5</v>
       </c>
-      <c r="X45" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC45" t="n">
+      <c r="AI45" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['12', '29', '50']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45667.6875</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6348,80 +6348,80 @@
         <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S46" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T46" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V46" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="X46" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['12', '29', '50']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI46" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ46" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45667.6875</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,16 +6448,16 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6474,65 +6474,65 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S47" t="n">
         <v>2.63</v>
       </c>
-      <c r="O47" t="n">
+      <c r="T47" t="n">
         <v>3.25</v>
       </c>
-      <c r="P47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.36</v>
       </c>
-      <c r="S47" t="n">
+      <c r="X47" t="n">
         <v>3</v>
       </c>
-      <c r="T47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z47" t="n">
         <v>1.62</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45667.6875</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="O49" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
         <v>1.62</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AC49" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG49" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AH49" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AJ49" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45667.6875</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="M50" t="n">
-        <v>3.48</v>
+        <v>4.48</v>
       </c>
       <c r="N50" t="n">
-        <v>3.94</v>
+        <v>7.4</v>
       </c>
       <c r="O50" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P50" t="n">
         <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T50" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W50" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45667.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="M52" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S52" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T52" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U52" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V52" t="n">
         <v>1.06</v>
       </c>
       <c r="W52" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X52" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="Y52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z52" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AA52" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AC52" t="n">
         <v>2</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['46', '79']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45667.69791666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O53" t="n">
         <v>3.2</v>
       </c>
-      <c r="N53" t="n">
-        <v>3</v>
-      </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U53" t="n">
         <v>1.53</v>
       </c>
-      <c r="S53" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V53" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>1.59</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['46', '79']</t>
+          <t>['12', '79']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '8', '19']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AI53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ53" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45667.69791666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N54" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O54" t="n">
         <v>2.5</v>
       </c>
-      <c r="O54" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P54" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R54" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="S54" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U54" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W54" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="X54" t="n">
-        <v>5</v>
+        <v>3.26</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.37</v>
+        <v>3.67</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AD54" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['12', '79']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['1', '8', '19']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45667.69791666666</v>
